--- a/TESTS/zlit_6_mify.xlsx
+++ b/TESTS/zlit_6_mify.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Давній розповідний твір що пояснює походження світу богів явищ природи — для стародавніх людей це була правда а не вигадка</t>
+          <t>Давній розповідний твір що пояснює походження світу богів явищ природи</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Вона стала основою європейської літератури мистецтва і науки — без знання грецьких міфів незрозуміла більшість класики</t>
+          <t>Вона стала основою європейської літератури мистецтва і науки</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Верховний бог Олімпу — владика богів і людей що керує блискавками і громом</t>
+          <t>Верховний бог Олімпу</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -706,7 +726,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Викрав вогонь у богів і подарував людям — це символ подарування знань і цивілізації людству</t>
+          <t>Викрав вогонь у богів і подарував людям</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -727,6 +747,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -748,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Зевс прикував його до скелі і щодня орел клював його печінку — яка відростала знову бо Прометей був безсмертний</t>
+          <t>Зевс прикував його до скелі і щодня орел клював його печінку</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -769,6 +794,11 @@
       <c r="H6" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Бунтівника-захисника людства що жертвує собою заради загального блага — символ альтруїзму і непокори тиранії</t>
+          <t>Бунтівника-захисника людства що жертвує собою заради загального блага</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Напівбог-герой якого Гера зненавиділа — Еврисфей наказав йому дванадцять неможливих подвигів</t>
+          <t>Напівбог-герой якого Гера зненавиділа</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -874,7 +914,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Дванадцять — він є символом фізичної і моральної сили що долає неможливе заради справедливості</t>
+          <t>Дванадцять</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -895,6 +935,11 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -939,6 +984,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Що незвичайне зробив малий Геракл ще в колисці?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заговорив</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Задушив двох змій, яких підіслала Гера</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Полетів</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Заснув на тиждень</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Чому богиня Гера зненавиділа Геракла з самого його народження?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він був злим</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Геракл був сином Зевса від смертної жінки, і Гера заздрила й гнівалась через це</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він украв у неї щось</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він образив її словами</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Що сталося з Гераклом через насланий Герою безум у дорослому віці?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого особливого</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>У нестямі він убив власних дітей, а опритомнівши, був приречений на спокутні подвиги</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він заснув на роки</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він втратив пам'ять назавжди</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Чому Геракл не міг убити Немейського лева звичайною зброєю?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лев був надто швидким</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Шкура лева не пробивалась ні мечем, ні стрілами</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лев був невидимим</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лев жив під водою</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Як Геракл зрештою здолав Немейського лева?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Отруїв його</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Задушив його голіруч</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Втопив його</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Спалив його</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Чому боротьба з Лернейською гідрою була особливо складною?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Гідра була невидимою</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>На місці кожної відрубаної голови виростали дві нові</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Гідра вміла говорити</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Гідра була надто маленькою</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>У чому полягала складність подвигу з Авгієвими стайнями?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Стайні охороняв дракон</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Стайні не чистили роками, і Гераклу треба було очистити їх за один день</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Стайні були порожні</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Стайні були під водою</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Як Геракл упорався із завданням очистити Авгієві стайні?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Найняв робітників</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Спрямував через стайні води двох річок, які змили весь бруд</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Спалив стайні</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Переніс стайні в інше місце</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>За яким подвигом Геракл мав здобути пояс Іпполіти?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Пояс простого селянина</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пояс цариці амазонок, легендарних жінок-воїнів</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пояс самого Зевса</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Пояс підводного царя</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>Для кого Дедал збудував на Криті величезний Лабіринт?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Для царя як палац</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Для утримання Мінотавра — чудовиська з тілом людини й головою бика</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Для зберігання скарбів</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Як в'язницю для людей</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Чому Дедал і його син Ікар опинились ув'язненими у власному Лабіринті?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони заблукали випадково</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Цар не хотів, щоб таємницю Лабіринту хтось видав, і утримував їх там</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони самі захотіли там жити</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Їх покарали боги</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Чому втеча морем чи суходолом була для Дедала і Ікара неможливою?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони боялись моря</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Цар Мінос пильно контролював усі шляхи з острова — і море, і суходіл</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони не вміли плавати</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Не було кораблів взагалі</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>З чого Дедал виготовив крила для себе і сина?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>З тканини й дерева</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>З пташиного пір'я, скріпленого воском</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>З металу</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>З листя</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Якого попередження Дедал дав Ікару перед польотом?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не літати взагалі</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Не підніматися надто високо до сонця і не опускатися надто низько до моря</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Летіти лише вночі</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Летіти повільно</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Чому застереження «не наближатись до сонця» було критично важливим?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Сонце засліплювало</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Тепло сонця могло розплавити віск, що скріплював крила</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сонце приваблювало птахів-хижаків</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Це була просто прикмета</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>У чому полягало покарання Прометея за крадіжку вогню для людей?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вигнання з Олімпу назавжди</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Зевс наказав прикувати його до скелі, де орел щодня виїдав йому печінку, яка відростала знову</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Перетворення на камінь</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Позбавлення мови</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому покарання Прометея описують як нескінченне?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Воно тривало рік</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Його печінка щоразу відростала знову, тож страждання повторювались день у день</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Орел був безсмертним</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Скеля рухалась</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Хто, за переказами, зрештою звільнив Прометея від мук?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Зевс сам пожалів його</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Герой Геракл, убивши орла-мучителя</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Сам Прометей утік</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Ніхто, він залишився прикутим назавжди</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Як давньогрецькі міфи вплинули на сучасну мову й науку, наприклад астрономію?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Ніяк не вплинули</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Багато сузір'їв, понять і термінів названо на честь персонажів мифів</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише на географію</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лише на музику</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чому образ Прометея став символом для митців і науковців пізніших епох?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо він був найсильнішим</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо він уособлює бунт заради прогресу і знань, навіть ціною особистих страждань</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо він був найбагатшим</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо про нього найбільше мифів</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Чому історія Ікара досі використовується як метафора в сучасній мові?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо це історія про політ</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вона символізує небезпеку надмірної амбіції чи нехтування попередженнями</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо Ікар був дуже молодим</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо це найдавніший міф</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>А</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що означає слово «лабіринт» і звідки воно походить?</t>
+          <t>Слово «лабіринт» походить від назви критської споруди, побудованої Дедалом для Мінотавра.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Яку роль відіграють давньогрецькі герої у порівнянні з богами?</t>
+          <t>На відміну від богів, давньогрецькі герої — смертні або напівбоги, що здобувають славу через подвиги й випробування.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Що таке «прометеїзм» як культурне поняття?</t>
+          <t>«Прометеїзм» — поняття, що означає сліпу покору богам без жодного бунту.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Яка мораль міфу про Дедала і Ікара?</t>
+          <t>Мораль міфу про Дедала і Ікара — варто слухати мудрі попередження, а не діяти необачно через надмірну впевненість.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,21 +2244,19 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Що символізує образ Ікара у світовій культурі?</t>
+          <t>Образ Ікара в культурі символізує надмірну амбіційність, що призводить до падіння.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>А</t>
@@ -2091,6 +2265,11 @@
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,29 +2281,32 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Що спільного між Прометеєм і Дедалом як культурними героями?</t>
+          <t>Прометей і Дедал не мають нічого спільного — один бог, інший простий смертний без жодних талантів.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які риси давньогрецького героя виявляються у цих міфах?</t>
+          <t>Що сталося з персонажами цих мифів?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Надлюдська сила або геній</t>
+          <t>Прометея прикували до скелі</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Готовність до жертви</t>
+          <t>Геракл здійснив дванадцять подвигів</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Безсмертя</t>
+          <t>Ікар успішно долетів додому</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Боротьба з несправедливістю</t>
+          <t>Ікар впав у море</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2295,6 +2492,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2337,6 +2539,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Він не послухав батька і злетів занадто близько до сонця — від спеки віск розтопився і він упав у море</t>
+          <t>Він не послухав батька і злетів занадто близько до сонця</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
